--- a/data/content/allocation_norms/NCF_adapted_for_Aruvi.xlsx
+++ b/data/content/allocation_norms/NCF_adapted_for_Aruvi.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10707"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10721"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kumar_radhakrishnan/main/kumar/AI/aruvi-saas/data/content/allocation_norms/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{535A5462-7EF4-F14C-A6C7-C755A3EECB19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ABC9E56-C746-8644-B5C0-C471F7A992B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13320" yWindow="600" windowWidth="13200" windowHeight="17400" xr2:uid="{ADA3B3B9-A2B6-284F-86B7-2C69879F5859}"/>
+    <workbookView xWindow="12440" yWindow="2500" windowWidth="13200" windowHeight="17400" xr2:uid="{ADA3B3B9-A2B6-284F-86B7-2C69879F5859}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="5" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="14">
   <si>
     <t>Science</t>
   </si>
@@ -88,6 +88,9 @@
   </si>
   <si>
     <t>Calibrated periods</t>
+  </si>
+  <si>
+    <t>RBS 2026-27 calendar</t>
   </si>
 </sst>
 </file>
@@ -579,7 +582,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="C3:M27"/>
+  <dimension ref="C3:M35"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="10.83203125" style="2"/>
@@ -808,6 +811,92 @@
         <v>440</v>
       </c>
     </row>
+    <row r="29" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="E29" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="30" spans="3:6" ht="29" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D30" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="3:6" ht="29" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C31" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="D31" s="4">
+        <v>150</v>
+      </c>
+      <c r="E31" s="4">
+        <v>180</v>
+      </c>
+      <c r="F31" s="4">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="32" spans="3:6" ht="29" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C32" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D32" s="4">
+        <v>150</v>
+      </c>
+      <c r="E32" s="4">
+        <v>150</v>
+      </c>
+      <c r="F32" s="4">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="33" spans="3:6" ht="29" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C33" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D33" s="4">
+        <v>270</v>
+      </c>
+      <c r="E33" s="4">
+        <v>150</v>
+      </c>
+      <c r="F33" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="3:6" ht="29" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C34" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34" s="4">
+        <v>0</v>
+      </c>
+      <c r="E34" s="4">
+        <v>0</v>
+      </c>
+      <c r="F34" s="4">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="35" spans="3:6" ht="29" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C35" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D35" s="4">
+        <v>240</v>
+      </c>
+      <c r="E35" s="4">
+        <v>150</v>
+      </c>
+      <c r="F35" s="4">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="65" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
